--- a/data/Rickenbach (LU)/cost/total_demand.xlsx
+++ b/data/Rickenbach (LU)/cost/total_demand.xlsx
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>189252.352522921</v>
+        <v>7885.51468845504</v>
       </c>
     </row>
     <row r="3">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>100305.6449016535</v>
+        <v>4179.40187090223</v>
       </c>
     </row>
     <row r="4">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>599778.6071011528</v>
+        <v>24990.77529588137</v>
       </c>
     </row>
   </sheetData>
